--- a/healthcare_forms/048_survey_feedback--healthcare_forms.xlsx
+++ b/healthcare_forms/048_survey_feedback--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>What did you like most about this form?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>second_section</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Do you like this form?</t>
+          <t>What did you least like about this form?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,24 +584,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Why did you like this form?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Please explain</t>
-        </is>
-      </c>
+          <t>Do you think this form is user-friendly?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -611,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Why did you not like this form?</t>
+          <t>How would you rate the clarity of this form's instructions?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_question_group</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Question Group 1</t>
+          <t>Which browser are you using?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,24 +653,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What browser are you using?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Please select the browser you are using</t>
-        </is>
-      </c>
+          <t>When did you take this survey?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -684,24 +676,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>When did you take this survey?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Date and time</t>
-        </is>
-      </c>
+          <t>What time did you take this survey?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -711,24 +699,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What time did you take this survey?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Time of day</t>
-        </is>
-      </c>
+          <t>Is this question a required field?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -738,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Is this a required field?</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -766,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is your email?</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -784,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your phone?</t>
+          <t>Do you have any additional comments or suggestions?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -807,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>First Question Group</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -835,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>second_question_group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>First Question Group</t>
+          <t>Second Question Group</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -858,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>first_question_group</t>
+          <t>third_question_group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -881,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Second Question Group</t>
+          <t>Third Question Group</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>first_question_group_2</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Question Group 2</t>
+          <t>Fourth Question Group</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -922,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Third Question Group</t>
+          <t>Fifth Question Group</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -945,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>first_question_group_3</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Question Group 1</t>
+          <t>Sixth Question Group</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -968,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -978,126 +962,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fourth Question Group</t>
+          <t>First Question Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>first_question_group_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Question Group 1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Fifth Question Group</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>first_question_group_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Question Group 1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sixth Question Group</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>first_question_group_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Question Group 1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1114,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1164,318 +1033,284 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_question_group_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1', 'label': 'Option 1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_question_group_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2', 'label': 'Option 2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chrome',_'label':_'chrome'}</t>
+          <t>chrome</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chrome', 'label': 'Chrome'}</t>
+          <t>Chrome</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'firefox',_'label':_'firefox'}</t>
+          <t>firefox</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'firefox', 'label': 'Firefox'}</t>
+          <t>Firefox</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>first_question_group_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>first_question_group_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>first_question_group_2_choices</t>
+          <t>third_question_group_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1', 'label': 'Option 1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>first_question_group_2_choices</t>
+          <t>third_question_group_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2', 'label': 'Option 2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>first_question_group_3_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>first_question_group_3_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>first_question_group_4_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>first_question_group_4_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>first_question_group_5_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>first_question_group_5_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>first_question_group_6_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>first_question_group_6_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
